--- a/branches/develop/StructureDefinition-mii-lm-person.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-person.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/develop/StructureDefinition-mii-lm-person.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-person.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-dev</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/develop/StructureDefinition-mii-lm-person.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3805" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -1152,61 +1152,6 @@
   </si>
   <si>
     <t>Patient.identifier:versicherungsnummer_pkv</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn</t>
-  </si>
-  <si>
-    <t>Person, die an einer Studie teilnimmt (unter Umständen, während sie Patient:in in einer Gesundheitseinrichtung ist)</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.id</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.extension</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.modifierExtension</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.SubjektIdentifizierungscode</t>
-  </si>
-  <si>
-    <t>Eindeutiger Identifikator eines Patienten im Kontext eines Forschungsprojekts (klinische Studie, Use Case)</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.Rechtsgrundlage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Consent)
-</t>
-  </si>
-  <si>
-    <t>Rechtsgrundlage (z.B. Einwilligung) aufgrund die PatientIn in die Studie eingeschlossen werden darf.</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.BeginnTeilnahme</t>
-  </si>
-  <si>
-    <t>Beginn der Teilnahme der Person an der Studie.</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.EndeTeilnahme</t>
-  </si>
-  <si>
-    <t>Ende der Teilnahme der Person an der Studie.</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.StatusDerTeilnahme</t>
-  </si>
-  <si>
-    <t>Stand der Teilnahme einer Person an der Studie, z.B. eingeschlossen, widerrufen, abgeschlossen etc.</t>
-  </si>
-  <si>
-    <t>Person.ProbandIn.BezeichnungDerStudie</t>
-  </si>
-  <si>
-    <t>Identifikator der Studie</t>
   </si>
   <si>
     <t>Person.PatientInPseudonym</t>
@@ -1536,7 +1481,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL123"/>
+  <dimension ref="A1:AL113"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.54296875" customWidth="true" bestFit="true"/>
@@ -13624,1075 +13569,9 @@
         <v>76</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AL123" t="s" s="2">
         <v>76</v>
       </c>
     </row>

--- a/branches/develop/StructureDefinition-mii-lm-person.xlsx
+++ b/branches/develop/StructureDefinition-mii-lm-person.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
